--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>Общо</t>
+  </si>
+  <si>
+    <t>Забележка:</t>
+  </si>
+  <si>
+    <t>Разходът е по проект №BG05SFPR002-2.012-0094-СО1 „Иновативни здравно-социални услуги в домашна среда“ по процедура BG05SFPR002-2.012 „Иновативни здравно-социални услуги“, Програма „Развитие на човешките ресурси” 2021-2027</t>
   </si>
 </sst>
 </file>
@@ -149,7 +155,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,12 +165,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,24 +208,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -783,9 +789,34 @@
         <v>63.08</v>
       </c>
     </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A14:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -97,6 +97,12 @@
     <t>3232526529 3232526529</t>
   </si>
   <si>
+    <t>Забележка:</t>
+  </si>
+  <si>
+    <t>Разходът е по проект №BG05SFPR002-2.012-0094-СО1 „Иновативни здравно-социални услуги в домашна среда“ по процедура BG05SFPR002-2.012 „Иновативни здравно-социални услуги“, Програма „Развитие на човешките ресурси” 2021-2027</t>
+  </si>
+  <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 5 - ПДГ</t>
   </si>
   <si>
@@ -113,12 +119,6 @@
   </si>
   <si>
     <t>Общо</t>
-  </si>
-  <si>
-    <t>Забележка:</t>
-  </si>
-  <si>
-    <t>Разходът е по проект №BG05SFPR002-2.012-0094-СО1 „Иновативни здравно-социални услуги в домашна среда“ по процедура BG05SFPR002-2.012 „Иновативни здравно-социални услуги“, Програма „Развитие на човешките ресурси” 2021-2027</t>
   </si>
 </sst>
 </file>
@@ -215,6 +215,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -226,12 +232,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -725,98 +725,97 @@
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:14">
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="C12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B13" s="9">
         <v>80.54000000000001</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C13" s="9">
         <v>3</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D13" s="10">
         <v>0.7733</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E13" s="9">
         <v>62.28</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F13" s="9">
         <v>63.08</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="10">
+    <row r="14" spans="1:14">
+      <c r="A14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="12">
         <v>80.54000000000001</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C14" s="12">
         <v>3</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
+      <c r="D14" s="10"/>
+      <c r="E14" s="12">
         <v>62.28</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F14" s="12">
         <v>63.08</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="25" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" ht="25" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A14:F15"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,19 +46,16 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В2764ТА</t>
@@ -79,22 +73,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:35:00</t>
-  </si>
-  <si>
-    <t>07:49:00</t>
-  </si>
-  <si>
-    <t>3232160372 3232160372</t>
-  </si>
-  <si>
-    <t>3232194520 3232194520</t>
-  </si>
-  <si>
-    <t>3232526529 3232526529</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -526,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,17 +514,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,243 +555,332 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>25.65</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H2">
+        <v>18.72</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J2">
+        <v>18.98</v>
+      </c>
+      <c r="K2">
+        <v>57550</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>18.48</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J3">
+        <v>18.84</v>
+      </c>
+      <c r="K3">
+        <v>58900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H4">
+        <v>21.9</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J4">
+        <v>22.2</v>
+      </c>
+      <c r="K4">
+        <v>58900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H5">
+        <v>18.36</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J5">
+        <v>18.72</v>
+      </c>
+      <c r="K5">
+        <v>57760</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F6">
+        <v>28.46</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6">
+        <v>20.21</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J6">
+        <v>20.49</v>
+      </c>
+      <c r="K6">
+        <v>57860</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>29.83</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H7">
+        <v>20.88</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="J7">
+        <v>21.18</v>
+      </c>
+      <c r="K7">
+        <v>59250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>24.22</v>
-      </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="11" spans="1:11" ht="25" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>0.78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>18.89</v>
-      </c>
-      <c r="J2">
-        <v>0.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>19.13</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" ht="25" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>57300</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46163</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="9">
+        <v>113.94</v>
+      </c>
+      <c r="C16" s="9">
+        <v>4</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.7171</v>
+      </c>
+      <c r="E16" s="9">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="F16" s="9">
+        <v>82.84999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>29.05</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>22.66</v>
-      </c>
-      <c r="J3">
-        <v>0.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>22.95</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>58230</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>27.27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>0.76</v>
-      </c>
-      <c r="I4" s="1">
-        <v>20.73</v>
-      </c>
-      <c r="J4">
-        <v>0.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
-        <v>58550</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
+      <c r="B17" s="9">
+        <v>24</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1.535</v>
+      </c>
+      <c r="E17" s="9">
+        <v>36.84</v>
+      </c>
+      <c r="F17" s="9">
+        <v>37.56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="25" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:14" ht="25" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="9">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="C13" s="9">
-        <v>3</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0.7733</v>
-      </c>
-      <c r="E13" s="9">
-        <v>62.28</v>
-      </c>
-      <c r="F13" s="9">
-        <v>63.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="12">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="C14" s="12">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12">
-        <v>62.28</v>
-      </c>
-      <c r="F14" s="12">
-        <v>63.08</v>
+      <c r="B18" s="12">
+        <v>137.94</v>
+      </c>
+      <c r="C18" s="12">
+        <v>6</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12">
+        <v>118.55</v>
+      </c>
+      <c r="F18" s="12">
+        <v>120.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:F9"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A11:F12"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Сливница</t>
@@ -74,6 +80,24 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>07:33</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -505,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,10 +542,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,22 +581,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46176</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>25.65</v>
@@ -587,25 +619,31 @@
       <c r="J2">
         <v>18.98</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
         <v>57550</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>214307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46176</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -622,25 +660,31 @@
       <c r="J3">
         <v>18.84</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
         <v>58900</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>214459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -657,25 +701,31 @@
       <c r="J4">
         <v>22.2</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>58900</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>214461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46181</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>12</v>
@@ -692,25 +742,31 @@
       <c r="J5">
         <v>18.72</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
         <v>57760</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>273457</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46182</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>28.46</v>
@@ -727,25 +783,31 @@
       <c r="J6">
         <v>20.49</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
         <v>57860</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>140333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46183</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>29.83</v>
@@ -762,18 +824,24 @@
       <c r="J7">
         <v>21.18</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
         <v>59250</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M7">
+        <v>217038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="25" customHeight="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -781,7 +849,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="25" customHeight="1">
+    <row r="12" spans="1:13" ht="25" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -789,9 +857,9 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -799,18 +867,18 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>7</v>
@@ -819,9 +887,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="A16" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" s="9">
         <v>113.94</v>
@@ -841,7 +909,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17" s="9">
         <v>24</v>
@@ -861,7 +929,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B18" s="12">
         <v>137.94</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -49,21 +49,15 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>Варна Порт</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
     <t>В2764ТА</t>
   </si>
   <si>
@@ -79,25 +73,16 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>15:56</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>15:49</t>
-  </si>
-  <si>
-    <t>07:33</t>
+    <t>2026-06-16 13:08:40</t>
+  </si>
+  <si>
+    <t>2026-06-17 12:48:06</t>
+  </si>
+  <si>
+    <t>2026-06-23 15:25:19</t>
+  </si>
+  <si>
+    <t>2026-06-24 12:41:54</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -529,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,12 +527,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,374 +564,242 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>28.28</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H2">
+        <v>18.66</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J2">
+        <v>18.95</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3">
+        <v>26.87</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H3">
+        <v>17.73</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J3">
+        <v>18</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>25.65</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H2">
-        <v>18.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J2">
-        <v>18.98</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>57550</v>
-      </c>
-      <c r="M2">
-        <v>214307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H3">
-        <v>18.48</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J3">
-        <v>18.84</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>58900</v>
-      </c>
-      <c r="M3">
-        <v>214459</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
-        <v>46176</v>
+        <v>46196</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
       <c r="G4" s="1">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>21.9</v>
+        <v>19.5</v>
       </c>
       <c r="I4" s="1">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>22.2</v>
+        <v>19.8</v>
       </c>
       <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>29.15</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>18.95</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>19.24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L4">
-        <v>58900</v>
-      </c>
-      <c r="M4">
-        <v>214461</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="25" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H5">
-        <v>18.36</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J5">
-        <v>18.72</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>57760</v>
-      </c>
-      <c r="M5">
-        <v>273457</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>28.46</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H6">
-        <v>20.21</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J6">
-        <v>20.49</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>57860</v>
-      </c>
-      <c r="M6">
-        <v>140333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>29.83</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="H7">
-        <v>20.88</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="J7">
-        <v>21.18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>59250</v>
-      </c>
-      <c r="M7">
-        <v>217038</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="9">
+        <v>114.3</v>
+      </c>
+      <c r="C14" s="9">
+        <v>4</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.6548</v>
+      </c>
+      <c r="E14" s="9">
+        <v>74.84</v>
+      </c>
+      <c r="F14" s="9">
+        <v>75.98999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="9">
-        <v>113.94</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B15" s="12">
+        <v>114.3</v>
+      </c>
+      <c r="C15" s="12">
         <v>4</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.7171</v>
-      </c>
-      <c r="E16" s="9">
-        <v>81.70999999999999</v>
-      </c>
-      <c r="F16" s="9">
-        <v>82.84999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="9">
-        <v>24</v>
-      </c>
-      <c r="C17" s="9">
-        <v>2</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1.535</v>
-      </c>
-      <c r="E17" s="9">
-        <v>36.84</v>
-      </c>
-      <c r="F17" s="9">
-        <v>37.56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="12">
-        <v>137.94</v>
-      </c>
-      <c r="C18" s="12">
-        <v>6</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12">
-        <v>118.55</v>
-      </c>
-      <c r="F18" s="12">
-        <v>120.41</v>
+      <c r="D15" s="10"/>
+      <c r="E15" s="12">
+        <v>74.84</v>
+      </c>
+      <c r="F15" s="12">
+        <v>75.98999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:F12"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,13 +52,22 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>В2764ТА</t>
@@ -73,16 +85,37 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 13:08:40</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:48:06</t>
-  </si>
-  <si>
-    <t>2026-06-23 15:25:19</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:41:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:08:00</t>
+  </si>
+  <si>
+    <t>12:47:00</t>
+  </si>
+  <si>
+    <t>15:25:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>12:18:00</t>
+  </si>
+  <si>
+    <t>3233446407 3233446407</t>
+  </si>
+  <si>
+    <t>3233483252 3233483252</t>
+  </si>
+  <si>
+    <t>3233764284 3233764284</t>
+  </si>
+  <si>
+    <t>3233820351 3233820351</t>
+  </si>
+  <si>
+    <t>3234076444 3234076444</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -514,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -523,14 +556,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,242 +600,331 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>28.28</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
         <v>0.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>18.66</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.67</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>18.95</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>58150</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46190</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>26.87</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
         <v>0.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>17.73</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.67</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>59600</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46196</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>19.5</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>19.8</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>59960</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>29.15</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5">
         <v>0.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>18.95</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.66</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>19.24</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5">
+        <v>58450</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s">
+      <c r="F6">
+        <v>26.85</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="25" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="25" customHeight="1">
-      <c r="A10" s="5"/>
+      <c r="H6">
+        <v>0.65</v>
+      </c>
+      <c r="I6" s="1">
+        <v>17.45</v>
+      </c>
+      <c r="J6">
+        <v>0.66</v>
+      </c>
+      <c r="K6" s="1">
+        <v>17.72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6">
+        <v>58720</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="9">
-        <v>114.3</v>
-      </c>
-      <c r="C14" s="9">
-        <v>4</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.6548</v>
-      </c>
-      <c r="E14" s="9">
-        <v>74.84</v>
-      </c>
-      <c r="F14" s="9">
-        <v>75.98999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="12">
-        <v>114.3</v>
-      </c>
-      <c r="C15" s="12">
-        <v>4</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="12">
-        <v>74.84</v>
-      </c>
-      <c r="F15" s="12">
-        <v>75.98999999999999</v>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="9">
+        <v>141.15</v>
+      </c>
+      <c r="C15" s="9">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.6538</v>
+      </c>
+      <c r="E15" s="9">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="F15" s="9">
+        <v>93.70999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="12">
+        <v>141.15</v>
+      </c>
+      <c r="C16" s="12">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="F16" s="12">
+        <v>93.70999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,16 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В2764ТА</t>
@@ -85,37 +79,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:08:00</t>
-  </si>
-  <si>
-    <t>12:47:00</t>
-  </si>
-  <si>
-    <t>15:25:00</t>
-  </si>
-  <si>
-    <t>12:41:00</t>
-  </si>
-  <si>
-    <t>12:18:00</t>
-  </si>
-  <si>
-    <t>3233446407 3233446407</t>
-  </si>
-  <si>
-    <t>3233483252 3233483252</t>
-  </si>
-  <si>
-    <t>3233764284 3233764284</t>
-  </si>
-  <si>
-    <t>3233820351 3233820351</t>
-  </si>
-  <si>
-    <t>3234076444 3234076444</t>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>12:18</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -547,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -556,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,238 +581,220 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
       </c>
       <c r="F2">
         <v>28.28</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
+      <c r="G2" s="1">
+        <v>0.66</v>
       </c>
       <c r="H2">
-        <v>0.66</v>
+        <v>18.66</v>
       </c>
       <c r="I2" s="1">
-        <v>18.66</v>
+        <v>0.67</v>
       </c>
       <c r="J2">
-        <v>0.67</v>
-      </c>
-      <c r="K2" s="1">
         <v>18.95</v>
       </c>
-      <c r="L2" t="s">
-        <v>24</v>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>58150</v>
       </c>
       <c r="M2">
-        <v>58150</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>275732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46190</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>26.87</v>
       </c>
-      <c r="G3" t="s">
-        <v>23</v>
+      <c r="G3" s="1">
+        <v>0.66</v>
       </c>
       <c r="H3">
-        <v>0.66</v>
+        <v>17.73</v>
       </c>
       <c r="I3" s="1">
-        <v>17.73</v>
+        <v>0.67</v>
       </c>
       <c r="J3">
-        <v>0.67</v>
-      </c>
-      <c r="K3" s="1">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
-        <v>25</v>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>59600</v>
       </c>
       <c r="M3">
-        <v>59600</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>114373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46196</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>19.5</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>19.8</v>
+      </c>
+      <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="H4">
-        <v>0.65</v>
-      </c>
-      <c r="I4" s="1">
-        <v>19.5</v>
-      </c>
-      <c r="J4">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
-        <v>19.8</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
+      <c r="L4">
+        <v>59960</v>
       </c>
       <c r="M4">
-        <v>59960</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>223057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
       </c>
       <c r="F5">
         <v>29.15</v>
       </c>
-      <c r="G5" t="s">
-        <v>23</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>18.95</v>
       </c>
       <c r="I5" s="1">
-        <v>18.95</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>19.24</v>
       </c>
-      <c r="L5" t="s">
-        <v>27</v>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>58450</v>
       </c>
       <c r="M5">
-        <v>58450</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>277954</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46203</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
       </c>
       <c r="F6">
         <v>26.85</v>
       </c>
-      <c r="G6" t="s">
-        <v>23</v>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6">
-        <v>0.65</v>
+        <v>17.45</v>
       </c>
       <c r="I6" s="1">
-        <v>17.45</v>
+        <v>0.66</v>
       </c>
       <c r="J6">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
         <v>17.72</v>
       </c>
-      <c r="L6" t="s">
-        <v>28</v>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>58720</v>
       </c>
       <c r="M6">
-        <v>58720</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>122502</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="25" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="25" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -845,7 +802,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:14" ht="25" customHeight="1">
+    <row r="11" spans="1:13" ht="25" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -853,9 +810,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -863,29 +820,29 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="9">
         <v>141.15</v>
@@ -903,9 +860,9 @@
         <v>93.70999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:13">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B16" s="12">
         <v>141.15</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,16 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В2763ТА</t>
@@ -73,28 +79,40 @@
     <t>78970155027722002</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-02 15:55:08</t>
-  </si>
-  <si>
-    <t>2026-07-02 16:20:35</t>
-  </si>
-  <si>
-    <t>2026-07-03 11:08:18</t>
-  </si>
-  <si>
-    <t>2026-07-06 13:23:40</t>
-  </si>
-  <si>
-    <t>2026-07-09 12:11:32</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:05:43</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:11:00</t>
+  </si>
+  <si>
+    <t>09:22:00</t>
+  </si>
+  <si>
+    <t>12:58:00</t>
+  </si>
+  <si>
+    <t>15:06:00</t>
+  </si>
+  <si>
+    <t>12:37:00</t>
+  </si>
+  <si>
+    <t>3234861521 3234861521</t>
+  </si>
+  <si>
+    <t>3234943237 3234943237</t>
+  </si>
+  <si>
+    <t>3235192307 3235192307</t>
+  </si>
+  <si>
+    <t>3235278234 3235278234</t>
+  </si>
+  <si>
+    <t>3235533944 3235533944</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -526,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,15 +553,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -580,350 +600,328 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>18.6</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>18.9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>61010</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>26.81</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
+        <v>0.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>16.89</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>17.16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>59460</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>17.64</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>28.86</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>0.63</v>
+      </c>
+      <c r="I4" s="1">
+        <v>18.18</v>
+      </c>
+      <c r="J4">
+        <v>0.64</v>
+      </c>
+      <c r="K4" s="1">
+        <v>18.47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>61360</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>60310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46205</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F5">
+        <v>25.7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>0.63</v>
+      </c>
+      <c r="I5" s="1">
+        <v>16.19</v>
+      </c>
+      <c r="J5">
+        <v>0.64</v>
+      </c>
+      <c r="K5" s="1">
+        <v>16.45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>59760</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>28.44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>0.63</v>
+      </c>
+      <c r="I6" s="1">
+        <v>17.92</v>
+      </c>
+      <c r="J6">
         <v>0.64</v>
       </c>
-      <c r="H3">
-        <v>19.2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J3">
-        <v>19.5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>60310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46206</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H4">
-        <v>17.64</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J4">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
-        <v>58880</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>26.86</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H5">
-        <v>16.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J5">
-        <v>16.92</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>58950</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46212</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H6">
-        <v>18.6</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J6">
-        <v>18.9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>60680</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>27.36</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H7">
-        <v>16.96</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J7">
-        <v>17.24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7">
-        <v>59220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="K6" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="L6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="25" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="M6">
+        <v>61690</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="25" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="9">
-        <v>114.22</v>
-      </c>
-      <c r="C16" s="9">
-        <v>4</v>
-      </c>
-      <c r="D16" s="10">
-        <v>0.6252</v>
-      </c>
-      <c r="E16" s="9">
-        <v>71.41</v>
-      </c>
-      <c r="F16" s="9">
-        <v>72.56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="9">
-        <v>24</v>
-      </c>
-      <c r="C17" s="9">
-        <v>2</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1.47</v>
-      </c>
-      <c r="E17" s="9">
-        <v>35.28</v>
-      </c>
-      <c r="F17" s="9">
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="12">
-        <v>138.22</v>
-      </c>
-      <c r="C18" s="12">
-        <v>6</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12">
-        <v>106.69</v>
-      </c>
-      <c r="F18" s="12">
-        <v>108.56</v>
+      <c r="B14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="9">
+        <v>139.81</v>
+      </c>
+      <c r="C15" s="9">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.6279</v>
+      </c>
+      <c r="E15" s="9">
+        <v>87.78</v>
+      </c>
+      <c r="F15" s="9">
+        <v>89.18000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="12">
+        <v>139.81</v>
+      </c>
+      <c r="C16" s="12">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12">
+        <v>87.78</v>
+      </c>
+      <c r="F16" s="12">
+        <v>89.18000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:F12"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -146,7 +146,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="10">
-        <v>0.6279</v>
+        <v>0.627852</v>
       </c>
       <c r="E15" s="9">
         <v>87.78</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="42">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -544,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -557,13 +560,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -606,235 +609,253 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>18.6</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>18.9</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
         <v>61010</v>
       </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>26.81</v>
+        <v>26.813</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>16.89</v>
-      </c>
       <c r="J3">
+        <v>16.89219</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>17.16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>17.16032</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
         <v>59460</v>
       </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46225</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>28.86</v>
+        <v>28.859</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>18.18</v>
-      </c>
       <c r="J4">
+        <v>18.18117</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>18.47</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>18.46976</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
         <v>61360</v>
       </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46227</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>25.7</v>
+        <v>25.703</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
         <v>0.63</v>
       </c>
-      <c r="I5" s="1">
-        <v>16.19</v>
-      </c>
       <c r="J5">
+        <v>16.19289</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.64</v>
       </c>
-      <c r="K5" s="1">
-        <v>16.45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>16.44992</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
         <v>59760</v>
       </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46232</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>28.44</v>
+        <v>28.438</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>0.63</v>
       </c>
-      <c r="I6" s="1">
-        <v>17.92</v>
-      </c>
       <c r="J6">
+        <v>17.91594</v>
+      </c>
+      <c r="K6" s="1">
         <v>0.64</v>
       </c>
-      <c r="K6" s="1">
-        <v>18.2</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>18.20032</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
         <v>61690</v>
       </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="25" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="25" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -842,7 +863,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:14" ht="25" customHeight="1">
+    <row r="11" spans="1:15" ht="25" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -850,9 +871,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -860,38 +881,38 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="9">
-        <v>139.81</v>
+        <v>139.813</v>
       </c>
       <c r="C15" s="9">
         <v>5</v>
       </c>
       <c r="D15" s="10">
-        <v>0.627852</v>
+        <v>0.627854</v>
       </c>
       <c r="E15" s="9">
         <v>87.78</v>
@@ -900,12 +921,12 @@
         <v>89.18000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="12">
-        <v>139.81</v>
+        <v>139.813</v>
       </c>
       <c r="C16" s="12">
         <v>5</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -147,9 +144,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -249,10 +246,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -560,13 +557,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,253 +606,235 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>18.6</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>18.9</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>18.6</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>18.9</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>61010</v>
       </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
       </c>
       <c r="F3">
         <v>26.813</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>16.892</v>
       </c>
       <c r="J3">
-        <v>16.89219</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>17.16032</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
+        <v>17.16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>59460</v>
       </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46225</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>28.859</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>18.181</v>
       </c>
       <c r="J4">
-        <v>18.18117</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>18.46976</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4">
+        <v>18.47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>61360</v>
       </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46227</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
       </c>
       <c r="F5">
         <v>25.703</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I5" s="1">
-        <v>0.63</v>
+        <v>16.193</v>
       </c>
       <c r="J5">
-        <v>16.19289</v>
+        <v>0.64</v>
       </c>
       <c r="K5" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L5" s="1">
-        <v>16.44992</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5">
+        <v>16.45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>59760</v>
       </c>
-      <c r="O5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46232</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>28.438</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I6" s="1">
-        <v>0.63</v>
+        <v>17.916</v>
       </c>
       <c r="J6">
-        <v>17.91594</v>
+        <v>0.64</v>
       </c>
       <c r="K6" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L6" s="1">
-        <v>18.20032</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6">
+        <v>18.2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
         <v>61690</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="25" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -863,7 +842,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:15" ht="25" customHeight="1">
+    <row r="11" spans="1:14" ht="25" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -871,9 +850,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -881,49 +860,49 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="9">
         <v>139.813</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>5</v>
       </c>
       <c r="D15" s="10">
-        <v>0.627854</v>
-      </c>
-      <c r="E15" s="9">
-        <v>87.78</v>
-      </c>
-      <c r="F15" s="9">
+        <v>0.628</v>
+      </c>
+      <c r="E15" s="10">
+        <v>87.782</v>
+      </c>
+      <c r="F15" s="10">
         <v>89.18000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="12">
         <v>139.813</v>
@@ -933,7 +912,7 @@
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="12">
-        <v>87.78</v>
+        <v>87.782</v>
       </c>
       <c r="F16" s="12">
         <v>89.18000000000001</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,61 +55,46 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>В2764ТА</t>
   </si>
   <si>
     <t>В2763ТА</t>
   </si>
   <si>
-    <t>В2764ТА</t>
+    <t>78970155027722002</t>
   </si>
   <si>
     <t>78970155027721996</t>
   </si>
   <si>
-    <t>78970155027722002</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>07:11:00</t>
-  </si>
-  <si>
-    <t>09:22:00</t>
-  </si>
-  <si>
-    <t>12:58:00</t>
-  </si>
-  <si>
-    <t>15:06:00</t>
-  </si>
-  <si>
-    <t>12:37:00</t>
-  </si>
-  <si>
-    <t>3234861521 3234861521</t>
-  </si>
-  <si>
-    <t>3234943237 3234943237</t>
-  </si>
-  <si>
-    <t>3235192307 3235192307</t>
-  </si>
-  <si>
-    <t>3235278234 3235278234</t>
-  </si>
-  <si>
-    <t>3235533944 3235533944</t>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>15:58</t>
+  </si>
+  <si>
+    <t>10:49</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -144,9 +126,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -246,10 +228,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -553,17 +535,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -603,16 +584,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -624,127 +602,118 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>18.24</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>18.6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>60030</v>
+      </c>
+      <c r="M2">
+        <v>158600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>0.62</v>
-      </c>
-      <c r="I2" s="1">
-        <v>18.6</v>
-      </c>
-      <c r="J2">
-        <v>0.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>18.9</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3">
+        <v>28.585</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H3">
+        <v>18.294</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="J3">
+        <v>18.58</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="M2">
-        <v>61010</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="L3">
+        <v>60030</v>
+      </c>
+      <c r="M3">
+        <v>158600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>26.813</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3">
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="1">
-        <v>16.892</v>
-      </c>
-      <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>17.16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>59460</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4">
-        <v>28.859</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
       </c>
       <c r="H4">
-        <v>0.63</v>
+        <v>18.24</v>
       </c>
       <c r="I4" s="1">
-        <v>18.181</v>
+        <v>1.55</v>
       </c>
       <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>18.47</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
+        <v>18.6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>62060</v>
       </c>
       <c r="M4">
-        <v>61360</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>242677</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -753,39 +722,36 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>25.703</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.63</v>
+        <v>19.5</v>
       </c>
       <c r="I5" s="1">
-        <v>16.193</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.64</v>
-      </c>
-      <c r="K5" s="1">
-        <v>16.45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
+        <v>19.8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>62060</v>
       </c>
       <c r="M5">
-        <v>59760</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>242681</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
-        <v>46232</v>
+        <v>46241</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -797,131 +763,189 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>28.438</v>
-      </c>
-      <c r="G6" t="s">
+        <v>21.985</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H6">
+        <v>14.29</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J6">
+        <v>14.51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>60260</v>
+      </c>
+      <c r="M6">
+        <v>137665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="H6">
-        <v>0.63</v>
-      </c>
-      <c r="I6" s="1">
-        <v>17.916</v>
-      </c>
-      <c r="J6">
-        <v>0.64</v>
-      </c>
-      <c r="K6" s="1">
-        <v>18.2</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="F7">
+        <v>28.212</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H7">
+        <v>18.338</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J7">
+        <v>18.62</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7">
+        <v>60520</v>
+      </c>
+      <c r="M7">
+        <v>291962</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M6">
-        <v>61690</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="25" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:14" ht="25" customHeight="1">
-      <c r="A11" s="5"/>
+    </row>
+    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="8" t="s">
+    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="9">
+        <v>108.782</v>
+      </c>
+      <c r="C16" s="9">
+        <v>4</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.64737</v>
+      </c>
+      <c r="E16" s="9">
+        <v>70.42</v>
+      </c>
+      <c r="F16" s="9">
+        <v>71.51000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="9">
-        <v>139.813</v>
-      </c>
-      <c r="C15" s="10">
-        <v>5</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0.628</v>
-      </c>
-      <c r="E15" s="10">
-        <v>87.782</v>
-      </c>
-      <c r="F15" s="10">
-        <v>89.18000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="12">
-        <v>139.813</v>
-      </c>
-      <c r="C16" s="12">
-        <v>5</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12">
-        <v>87.782</v>
-      </c>
-      <c r="F16" s="12">
-        <v>89.18000000000001</v>
+      <c r="B17" s="9">
+        <v>24</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10">
+        <v>1.52</v>
+      </c>
+      <c r="E17" s="9">
+        <v>36.48</v>
+      </c>
+      <c r="F17" s="9">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="12">
+        <v>132.782</v>
+      </c>
+      <c r="C18" s="12">
+        <v>6</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="12">
+        <v>106.9</v>
+      </c>
+      <c r="F18" s="12">
+        <v>108.71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A10:F11"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F12"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,16 +58,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В2764ТА</t>
@@ -79,22 +76,34 @@
     <t>78970155027721996</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>15:58</t>
-  </si>
-  <si>
-    <t>10:49</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:48:00</t>
+  </si>
+  <si>
+    <t>11:06:00</t>
+  </si>
+  <si>
+    <t>07:29:00</t>
+  </si>
+  <si>
+    <t>15:44:00</t>
+  </si>
+  <si>
+    <t>3236492437 3236492437</t>
+  </si>
+  <si>
+    <t>3236639843 3236639843</t>
+  </si>
+  <si>
+    <t>3236957825 3236957825</t>
+  </si>
+  <si>
+    <t>3237221728 3237221728</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -125,10 +134,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -208,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -228,10 +238,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,16 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -584,368 +597,281 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>22.33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>22.107</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>14.738</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>60720</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>28.42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I3" s="1">
+        <v>28.136</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>18.757</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>60980</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>18.24</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>18.6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
-        <v>60030</v>
-      </c>
-      <c r="M2">
-        <v>158600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46237</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="H4" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="1">
+        <v>29.7</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>62400</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>28.585</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H3">
-        <v>18.294</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J3">
-        <v>18.58</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>60030</v>
-      </c>
-      <c r="M3">
-        <v>158600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46239</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F5">
+        <v>25.92</v>
+      </c>
+      <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>18.24</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>18.6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>62060</v>
-      </c>
-      <c r="M4">
-        <v>242677</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46239</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="H5" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I5" s="1">
+        <v>25.661</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>17.107</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>62720</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5">
-        <v>19.5</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J5">
-        <v>19.8</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>62060</v>
-      </c>
-      <c r="M5">
-        <v>242681</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46241</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>21.985</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H6">
-        <v>14.29</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J6">
-        <v>14.51</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>60260</v>
-      </c>
-      <c r="M6">
-        <v>137665</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46246</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>28.212</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H7">
-        <v>18.338</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J7">
-        <v>18.62</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7">
-        <v>60520</v>
-      </c>
-      <c r="M7">
-        <v>291962</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="9">
-        <v>108.782</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B14" s="9">
+        <v>106.67</v>
+      </c>
+      <c r="C14" s="10">
         <v>4</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.64737</v>
-      </c>
-      <c r="E16" s="9">
-        <v>70.42</v>
-      </c>
-      <c r="F16" s="9">
-        <v>71.51000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="9">
-        <v>24</v>
-      </c>
-      <c r="C17" s="9">
-        <v>2</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1.52</v>
-      </c>
-      <c r="E17" s="9">
-        <v>36.48</v>
-      </c>
-      <c r="F17" s="9">
-        <v>37.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="12">
-        <v>132.782</v>
-      </c>
-      <c r="C18" s="12">
-        <v>6</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12">
-        <v>106.9</v>
-      </c>
-      <c r="F18" s="12">
-        <v>108.71</v>
+      <c r="D14" s="11">
+        <v>0.9900099999999999</v>
+      </c>
+      <c r="E14" s="9">
+        <v>105.6</v>
+      </c>
+      <c r="F14" s="9">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="13">
+        <v>106.67</v>
+      </c>
+      <c r="C15" s="14">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="13">
+        <v>105.6</v>
+      </c>
+      <c r="F15" s="13">
+        <v>70.40000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:F12"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -624,10 +624,10 @@
         <v>21</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>22.107</v>
+        <v>14.514</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -668,10 +668,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>28.136</v>
+        <v>18.473</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -712,10 +712,10 @@
         <v>21</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>29.7</v>
+        <v>19.5</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -756,10 +756,10 @@
         <v>21</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>25.661</v>
+        <v>16.848</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -841,10 +841,10 @@
         <v>4</v>
       </c>
       <c r="D14" s="11">
-        <v>0.9900099999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E14" s="9">
-        <v>105.6</v>
+        <v>69.33</v>
       </c>
       <c r="F14" s="9">
         <v>70.40000000000001</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="13">
-        <v>105.6</v>
+        <v>69.33</v>
       </c>
       <c r="F15" s="13">
         <v>70.40000000000001</v>
